--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050112</v>
       </c>
       <c r="B2" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93177</v>
+        <v>93180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050112</v>
       </c>
       <c r="B2" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93180</v>
+        <v>93186</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132214316</v>
       </c>
       <c r="B4" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050112</v>
       </c>
       <c r="B2" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93186</v>
+        <v>93196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132214316</v>
       </c>
       <c r="B4" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132050112</v>
       </c>
       <c r="B2" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93196</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>93198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>132214316</v>
       </c>
       <c r="B4" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93198</v>
+        <v>93200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45942-2025 artfynd.xlsx
+++ b/artfynd/A 45942-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>132214526</v>
       </c>
       <c r="B3" t="n">
-        <v>93200</v>
+        <v>93201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
